--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484317_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484317_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5984</v>
+        <v>5.1511</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9246</v>
+        <v>4.4501</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6738</v>
+        <v>0.701</v>
       </c>
       <c r="G2" t="n">
         <v>3.9614</v>
@@ -610,13 +610,13 @@
         <v>1.7581</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9723000000000001</v>
+        <v>-0.4196</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5172</v>
+        <v>0.0083</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4552</v>
+        <v>-0.4279</v>
       </c>
       <c r="V2" t="n">
         <v>1.2186</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SIMON</t>
+          <t>J. CANAL FERRER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5841</v>
+        <v>3.1082</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4985</v>
+        <v>1.4945</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0856</v>
+        <v>1.6137</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6628</v>
+        <v>2.104</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3421</v>
+        <v>0.3369</v>
       </c>
       <c r="I3" t="n">
-        <v>4.0049</v>
+        <v>1.7671</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9114</v>
+        <v>1.4449</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.0819</v>
       </c>
       <c r="L3" t="n">
-        <v>4.0061</v>
+        <v>1.363</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2485</v>
+        <v>0.6591</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2474</v>
+        <v>0.2551</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0012</v>
+        <v>0.4041</v>
       </c>
       <c r="P3" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3441</v>
+        <v>-0.1953</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9301</v>
+        <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6673</v>
+        <v>-1.0311</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7088</v>
+        <v>-0.0322</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0415</v>
+        <v>-0.9988</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3321</v>
+        <v>0.2772</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2224</v>
+        <v>0.2772</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CANAL FERRER</t>
+          <t>A. SIMON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1004</v>
+        <v>2.9821</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5956</v>
+        <v>2.3051</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5048</v>
+        <v>0.6771</v>
       </c>
       <c r="G4" t="n">
-        <v>2.104</v>
+        <v>2.6628</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3369</v>
+        <v>-1.3421</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7671</v>
+        <v>4.0049</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4449</v>
+        <v>3.9114</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0819</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>1.363</v>
+        <v>4.0061</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6591</v>
+        <v>-1.2485</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2551</v>
+        <v>-1.2474</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4041</v>
+        <v>-0.0012</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1953</v>
+        <v>-2.3441</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9534</v>
+        <v>2.9301</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0389</v>
+        <v>0.0653</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0689</v>
+        <v>0.5154</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1078</v>
+        <v>-0.4501</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2772</v>
+        <v>0.2224</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3358</v>
+        <v>2.8764</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8639</v>
+        <v>1.2683</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4719</v>
+        <v>1.6081</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3952</v>
@@ -844,13 +844,13 @@
         <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5463</v>
+        <v>-1.0056</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5915</v>
+        <v>-0.187</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9548</v>
+        <v>-0.8186</v>
       </c>
       <c r="V5" t="n">
         <v>2.7145</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2689</v>
+        <v>2.8022</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3455</v>
+        <v>3.7699</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0766</v>
+        <v>-0.9677</v>
       </c>
       <c r="G6" t="n">
         <v>4.0424</v>
@@ -922,13 +922,13 @@
         <v>1.9534</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3828</v>
+        <v>-0.8495</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2062</v>
+        <v>0.2182</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1767</v>
+        <v>-1.0677</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1295</v>
+        <v>1.7057</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7451</v>
+        <v>3.2396</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6156</v>
+        <v>-1.5339</v>
       </c>
       <c r="G7" t="n">
         <v>3.1957</v>
@@ -1000,13 +1000,13 @@
         <v>1.7581</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2306</v>
+        <v>-0.1933</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.4465</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7215</v>
+        <v>-0.6398</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8828</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2705</v>
+        <v>0.5818</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7753</v>
+        <v>-0.9465</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0458</v>
+        <v>1.5283</v>
       </c>
       <c r="G8" t="n">
         <v>2.4745</v>
@@ -1078,13 +1078,13 @@
         <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2311</v>
+        <v>-0.9197</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0151</v>
+        <v>-0.1863</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.216</v>
+        <v>-0.7335</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3869</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. VIDAL AGRA</t>
+          <t>O. SUBIRANAS CASELLAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.4146</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7415</v>
+        <v>-0.5456</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4245</v>
+        <v>0.131</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4168</v>
+        <v>1.4183</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3628</v>
+        <v>-0.8475</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0541</v>
+        <v>2.2659</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6616</v>
+        <v>1.3635</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2037</v>
+        <v>-0.6332</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.458</v>
+        <v>1.9966</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2448</v>
+        <v>0.0549</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1591</v>
+        <v>-0.2144</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4039</v>
+        <v>0.2692</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.575</v>
+        <v>-0.7277</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7705</v>
+        <v>-0.2682</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3455</v>
+        <v>-0.4596</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3321</v>
+        <v>-1.4959</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8279</v>
+        <v>-0.6642</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4959</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. SUBIRANAS CASELLAS</t>
+          <t>C. VIDAL AGRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7257</v>
+        <v>-0.5579</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7478</v>
+        <v>0.4581</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0221</v>
+        <v>-1.016</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4183</v>
+        <v>-1.4168</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8475</v>
+        <v>-1.3628</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2659</v>
+        <v>-0.0541</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3635</v>
+        <v>-1.6616</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6332</v>
+        <v>-1.2037</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9966</v>
+        <v>-0.458</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0549</v>
+        <v>0.2448</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2144</v>
+        <v>-0.1591</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2692</v>
+        <v>0.4039</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0389</v>
+        <v>-0.4499</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4704</v>
+        <v>0.4871</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5685</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="V10" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.8279</v>
+      </c>
+      <c r="X10" t="n">
         <v>-1.4959</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.6642</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.8317</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3875</v>
+        <v>-3.1386</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5932</v>
+        <v>-3.2899</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2058</v>
+        <v>0.1513</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2121</v>
@@ -1312,13 +1312,13 @@
         <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7847</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4099</v>
+        <v>-0.1065</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3748</v>
+        <v>-0.4293</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.4914</v>
+        <v>15.0964</v>
       </c>
       <c r="E12" t="n">
-        <v>11.5984</v>
+        <v>12.2036</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8931</v>
+        <v>2.8929</v>
       </c>
       <c r="G12" t="n">
         <v>15.835</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3493000000000003</v>
+        <v>-0.3493000000000002</v>
       </c>
       <c r="I12" t="n">
-        <v>16.18429999999999</v>
+        <v>16.1843</v>
       </c>
       <c r="J12" t="n">
         <v>16.7104</v>
@@ -1372,7 +1372,7 @@
         <v>14.8429</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8751000000000001</v>
+        <v>-0.8751</v>
       </c>
       <c r="N12" t="n">
         <v>-2.2165</v>
@@ -1381,7 +1381,7 @@
         <v>1.3414</v>
       </c>
       <c r="P12" t="n">
-        <v>4.883500000000001</v>
+        <v>4.8835</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.7205</v>
@@ -1390,22 +1390,22 @@
         <v>16.604</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.6721</v>
+        <v>-6.0669</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2900000000000002</v>
+        <v>0.8953</v>
       </c>
       <c r="U12" t="n">
         <v>-6.962300000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4447000000000001</v>
+        <v>0.4447</v>
       </c>
       <c r="W12" t="n">
-        <v>6.3183</v>
+        <v>6.318300000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.873799999999999</v>
+        <v>-5.8738</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3116</v>
+        <v>3.8015</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9846</v>
+        <v>3.2879</v>
       </c>
       <c r="F13" t="n">
-        <v>0.327</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>3.4734</v>
@@ -1468,13 +1468,13 @@
         <v>1.9534</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2413</v>
+        <v>1.7313</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9329</v>
+        <v>1.2362</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3085</v>
+        <v>0.495</v>
       </c>
       <c r="V13" t="n">
         <v>2.5037</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8716</v>
+        <v>1.8584</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.0361</v>
+        <v>0.7119</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9077</v>
+        <v>1.1464</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.263</v>
+        <v>0.5742</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.0867</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.4167</v>
+        <v>0.6609</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.3685</v>
+        <v>0.11</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8967000000000001</v>
+        <v>0.1228</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4718</v>
+        <v>-0.0128</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8945</v>
+        <v>0.4642</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0504</v>
+        <v>-0.2095</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9449</v>
+        <v>0.6737</v>
       </c>
       <c r="P14" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-1.9534</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2518</v>
+        <v>0.4209</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4541</v>
+        <v>0.3247</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7976</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8828</v>
+        <v>0.2772</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8317</v>
+        <v>0.2772</v>
       </c>
       <c r="X14" t="n">
-        <v>1.0511</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7512</v>
+        <v>0.6303</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.097</v>
+        <v>-2.1372</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8482</v>
+        <v>2.7674</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5742</v>
+        <v>-2.263</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0867</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6609</v>
+        <v>-1.4167</v>
       </c>
       <c r="J15" t="n">
-        <v>0.11</v>
+        <v>-1.3685</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1228</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0128</v>
+        <v>-0.4718</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4642</v>
+        <v>-0.8945</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2095</v>
+        <v>0.0504</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6737</v>
+        <v>-0.9449</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6862</v>
+        <v>1.0104</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4842</v>
+        <v>0.353</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.202</v>
+        <v>0.6574</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2772</v>
+        <v>1.8828</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>0.8317</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.0511</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1887</v>
+        <v>-1.9657</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9377</v>
+        <v>-0.489</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.749</v>
+        <v>-1.4766</v>
       </c>
       <c r="G16" t="n">
         <v>-2.3071</v>
@@ -1702,13 +1702,13 @@
         <v>0.3907</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9373</v>
+        <v>1.7829</v>
       </c>
       <c r="T16" t="n">
-        <v>4.295</v>
+        <v>1.8683</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3577</v>
+        <v>-0.0854</v>
       </c>
       <c r="V16" t="n">
         <v>0.1213</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3071</v>
+        <v>-2.1627</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7683</v>
+        <v>0.8583</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.0754</v>
+        <v>-3.021</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8912</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4121</v>
+        <v>0.5565</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7802</v>
+        <v>0.8702</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3681</v>
+        <v>-0.3137</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8279</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5565</v>
+        <v>-2.164</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0999</v>
+        <v>-0.8243</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.6565</v>
+        <v>-1.3397</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.4113</v>
+        <v>-4.3258</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1458</v>
+        <v>1.3651</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.2655</v>
+        <v>-5.6909</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8646</v>
+        <v>-1.2538</v>
       </c>
       <c r="K18" t="n">
-        <v>0.08309999999999999</v>
+        <v>2.0082</v>
       </c>
       <c r="L18" t="n">
-        <v>1.7815</v>
+        <v>-3.2619</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.2759</v>
+        <v>-3.072</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2289</v>
+        <v>-0.6431</v>
       </c>
       <c r="O18" t="n">
-        <v>-4.047</v>
+        <v>-2.4289</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7883</v>
+        <v>1.6694</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1888</v>
+        <v>1.129</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5996</v>
+        <v>0.5404</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1522</v>
+        <v>-0.875</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
         <v>-1.1522</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6811</v>
+        <v>-3.0662</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1276</v>
+        <v>0.9988</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5535</v>
+        <v>-4.065</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.3258</v>
+        <v>-2.4113</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3651</v>
+        <v>-0.1458</v>
       </c>
       <c r="I19" t="n">
-        <v>-5.6909</v>
+        <v>-2.2655</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2538</v>
+        <v>1.8646</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0082</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.2619</v>
+        <v>1.7815</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.072</v>
+        <v>-4.2759</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6431</v>
+        <v>-0.2289</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.4289</v>
+        <v>-4.047</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3674</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3441</v>
+        <v>1.1721</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1522</v>
+        <v>1.2787</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8256</v>
+        <v>1.0876</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3266</v>
+        <v>0.1911</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.875</v>
+        <v>-1.1522</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>-1.1522</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.6368</v>
+        <v>-3.5896</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.9586</v>
+        <v>-2.6441</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6782</v>
+        <v>-0.9455</v>
       </c>
       <c r="G20" t="n">
         <v>-4.7872</v>
@@ -2014,13 +2014,13 @@
         <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6034</v>
+        <v>0.4437</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8941</v>
+        <v>0.4204</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7094</v>
+        <v>0.0233</v>
       </c>
       <c r="V20" t="n">
         <v>1.3399</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.433</v>
+        <v>-5.811</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4643</v>
+        <v>-2.6554</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.9687</v>
+        <v>-3.1557</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8971</v>
@@ -2092,13 +2092,13 @@
         <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.8213</v>
+        <v>-0.1994</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1362</v>
+        <v>-0.3272</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6852</v>
+        <v>0.1278</v>
       </c>
       <c r="V21" t="n">
         <v>-2.7145</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-14.4914</v>
+        <v>-12.469</v>
       </c>
       <c r="E22" t="n">
         <v>-2.8931</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.5984</v>
+        <v>-9.5761</v>
       </c>
       <c r="G22" t="n">
         <v>-15.8351</v>
@@ -2149,7 +2149,7 @@
         <v>2.2166</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3414</v>
+        <v>-1.341399999999999</v>
       </c>
       <c r="M22" t="n">
         <v>-16.7103</v>
@@ -2170,19 +2170,19 @@
         <v>11.7205</v>
       </c>
       <c r="S22" t="n">
-        <v>6.672100000000001</v>
+        <v>8.6944</v>
       </c>
       <c r="T22" t="n">
-        <v>6.9621</v>
+        <v>6.9622</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2901</v>
+        <v>1.7321</v>
       </c>
       <c r="V22" t="n">
         <v>-0.4447000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>5.873699999999999</v>
+        <v>5.8737</v>
       </c>
       <c r="X22" t="n">
         <v>-6.3184</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484317_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484317_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.8317</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-5.8738</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-0.7653</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,11 +1707,16 @@
       <c r="X15" t="n">
         <v>1.0511</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>V. MARKOVETSKYY</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.9657</v>
+        <v>0.614</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.489</v>
+        <v>0.614</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4766</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.3071</v>
+        <v>0.614</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4994</v>
+        <v>0.614</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8077</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4039</v>
+        <v>0.614</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4848</v>
+        <v>0.614</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9032</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0146</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8887</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.7829</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8683</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0854</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1213</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1213</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>V. MARKOVETSKYY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1627</v>
+        <v>-1.9657</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8583</v>
+        <v>-0.489</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.021</v>
+        <v>-1.4766</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8912</v>
+        <v>-2.3071</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6621</v>
+        <v>-0.4994</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2292</v>
+        <v>-1.8077</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0119</v>
+        <v>-0.4039</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.4848</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5803</v>
+        <v>0.0809</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8793</v>
+        <v>-1.9032</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0698</v>
+        <v>-0.0146</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8095</v>
+        <v>-1.8887</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5565</v>
+        <v>1.7829</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8702</v>
+        <v>1.8683</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3137</v>
+        <v>-0.0854</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.8279</v>
+        <v>0.1213</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.8279</v>
+        <v>0.1213</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.164</v>
+        <v>-2.1627</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8243</v>
+        <v>0.8583</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3397</v>
+        <v>-3.021</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.3258</v>
+        <v>-0.8912</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3651</v>
+        <v>-0.6621</v>
       </c>
       <c r="I18" t="n">
-        <v>-5.6909</v>
+        <v>-0.2292</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2538</v>
+        <v>-0.0119</v>
       </c>
       <c r="K18" t="n">
-        <v>2.0082</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.2619</v>
+        <v>0.5803</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.072</v>
+        <v>-0.8793</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6431</v>
+        <v>-0.0698</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.4289</v>
+        <v>-0.8095</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6694</v>
+        <v>0.5565</v>
       </c>
       <c r="T18" t="n">
-        <v>1.129</v>
+        <v>0.8702</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5404</v>
+        <v>-0.3137</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.875</v>
+        <v>-1.8279</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1522</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0662</v>
+        <v>-2.778</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9988</v>
+        <v>-1.4382</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.065</v>
+        <v>-1.3397</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4113</v>
+        <v>-4.9398</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1458</v>
+        <v>0.7511</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.2655</v>
+        <v>-5.6909</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8646</v>
+        <v>-1.8677</v>
       </c>
       <c r="K19" t="n">
-        <v>0.08309999999999999</v>
+        <v>1.3942</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7815</v>
+        <v>-3.2619</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.2759</v>
+        <v>-3.072</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2289</v>
+        <v>-0.6431</v>
       </c>
       <c r="O19" t="n">
-        <v>-4.047</v>
+        <v>-2.4289</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1721</v>
+        <v>2.3441</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2787</v>
+        <v>1.6694</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0876</v>
+        <v>1.129</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1911</v>
+        <v>0.5404</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1522</v>
+        <v>-0.875</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
         <v>-1.1522</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5896</v>
+        <v>-3.0662</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6441</v>
+        <v>0.9988</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9455</v>
+        <v>-4.065</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.7872</v>
+        <v>-2.4113</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.82</v>
+        <v>-0.1458</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.9672</v>
+        <v>-2.2655</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.3297</v>
+        <v>1.8646</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1167</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.213</v>
+        <v>1.7815</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4575</v>
+        <v>-4.2759</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7032</v>
+        <v>-0.2289</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7542</v>
+        <v>-4.047</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4437</v>
+        <v>1.2787</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4204</v>
+        <v>1.0876</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0233</v>
+        <v>0.1911</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3399</v>
+        <v>-1.1522</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1213</v>
+        <v>-1.1522</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.811</v>
+        <v>-3.5896</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6554</v>
+        <v>-2.6441</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1557</v>
+        <v>-0.9455</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8971</v>
+        <v>-4.7872</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1591</v>
+        <v>-1.82</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.738</v>
+        <v>-2.9672</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3747</v>
+        <v>-2.3297</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2047</v>
+        <v>-1.1167</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5794</v>
+        <v>-1.213</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5225</v>
+        <v>-2.4575</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3638</v>
+        <v>-0.7032</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.1587</v>
+        <v>-1.7542</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.586</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1994</v>
+        <v>0.4437</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3272</v>
+        <v>0.4204</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1278</v>
+        <v>0.0233</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.7145</v>
+        <v>1.3399</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.7145</v>
+        <v>0.1213</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,68 +2226,152 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
+        <v>-5.811</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-2.6554</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-3.1557</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-2.8971</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.1591</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-2.738</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.3747</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.2047</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.5794</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-2.5225</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.3638</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-2.1587</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.1994</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.3272</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.1278</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-2.7145</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-2.7145</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484317_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
         <v>-12.469</v>
       </c>
-      <c r="E22" t="n">
-        <v>-2.8931</v>
-      </c>
-      <c r="F22" t="n">
+      <c r="E23" t="n">
+        <v>-2.893</v>
+      </c>
+      <c r="F23" t="n">
         <v>-9.5761</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G23" t="n">
         <v>-15.8351</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H23" t="n">
         <v>0.3490999999999997</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I23" t="n">
         <v>-16.1843</v>
       </c>
-      <c r="J22" t="n">
-        <v>0.8751</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="J23" t="n">
+        <v>0.8752000000000002</v>
+      </c>
+      <c r="K23" t="n">
         <v>2.2166</v>
       </c>
-      <c r="L22" t="n">
-        <v>-1.341399999999999</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="L23" t="n">
+        <v>-1.3414</v>
+      </c>
+      <c r="M23" t="n">
         <v>-16.7103</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N23" t="n">
         <v>-1.8673</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O23" t="n">
         <v>-14.843</v>
       </c>
-      <c r="P22" t="n">
-        <v>-4.883599999999999</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="P23" t="n">
+        <v>-4.8836</v>
+      </c>
+      <c r="Q23" t="n">
         <v>-16.604</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>11.7205</v>
       </c>
-      <c r="S22" t="n">
-        <v>8.6944</v>
-      </c>
-      <c r="T22" t="n">
-        <v>6.9622</v>
-      </c>
-      <c r="U22" t="n">
+      <c r="S23" t="n">
+        <v>8.694399999999998</v>
+      </c>
+      <c r="T23" t="n">
+        <v>6.962199999999999</v>
+      </c>
+      <c r="U23" t="n">
         <v>1.7321</v>
       </c>
-      <c r="V22" t="n">
-        <v>-0.4447000000000001</v>
-      </c>
-      <c r="W22" t="n">
-        <v>5.8737</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="V23" t="n">
+        <v>-0.4446999999999992</v>
+      </c>
+      <c r="W23" t="n">
+        <v>5.873699999999999</v>
+      </c>
+      <c r="X23" t="n">
         <v>-6.3184</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
